--- a/Assets/Resources/DataFiles/SkillData/ExcelFile/SkillData.xlsx
+++ b/Assets/Resources/DataFiles/SkillData/ExcelFile/SkillData.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -596,6 +596,84 @@
         <v>4</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GunnerArcBuster</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>아크 버스터</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ArcProjectile</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GunnerBombThrow</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>폭탄 투척</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BombThrow</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GunnerBackstepShot</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>백스탭 샷</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BackstepShot</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/SkillData/ExcelFile/SkillData.xlsx
+++ b/Assets/Resources/DataFiles/SkillData/ExcelFile/SkillData.xlsx
@@ -2,35 +2,66 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SkillData" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="6">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="00888888"/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -53,17 +84,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -426,56 +461,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19.3984375" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="9.8984375" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" customFormat="1" s="4">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
-    <row r="2">
+    <row r="2" customFormat="1" s="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>skillId</t>
@@ -509,6 +564,26 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>rangeWidthOrAngle</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>manaCost</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>evolution1ManaCost</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>evolution2ManaCost</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>evolution3ManaCost</t>
         </is>
       </c>
     </row>
@@ -540,6 +615,18 @@
       <c r="G3" t="n">
         <v>180</v>
       </c>
+      <c r="H3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -569,6 +656,18 @@
       <c r="G4" t="n">
         <v>2</v>
       </c>
+      <c r="H4" t="n">
+        <v>40</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,6 +694,18 @@
       <c r="F5" t="n">
         <v>4</v>
       </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -621,6 +732,18 @@
       <c r="F6" t="n">
         <v>12</v>
       </c>
+      <c r="H6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,6 +770,18 @@
       <c r="F7" t="n">
         <v>6</v>
       </c>
+      <c r="H7" t="n">
+        <v>40</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -672,6 +807,18 @@
       </c>
       <c r="F8" t="n">
         <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
